--- a/output/Summary.xlsx
+++ b/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,208 @@
         <v>1</v>
       </c>
       <c r="AE2" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>output\20251121173006-1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30960697.35755812</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4265505.792016438</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1936831.529638083</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6202337.321654522</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24758360.0359036</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>30960697.35755812</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>112.1920001506805</v>
+      </c>
+      <c r="X3" t="n">
+        <v>30960697.35755811</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>30960697.35755812</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.725290298461914e-09</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>output\20251121180622-1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30980978.20867186</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4367103.613949267</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1965408.474573259</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6332512.088522526</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24648466.12014933</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>30980978.20867186</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>118.3270001411438</v>
+      </c>
+      <c r="X4" t="n">
+        <v>30980978.20867186</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>30980978.20867186</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/output/Summary.xlsx
+++ b/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE4"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,6 +885,915 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>output\20251124154118-1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>30950812.56848679</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4359169.152210644</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1963377.311450375</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6322546.463661019</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24628266.10482577</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30950812.56848679</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>127.7699999809265</v>
+      </c>
+      <c r="X5" t="n">
+        <v>30950812.56848677</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>30950812.56848679</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.60770320892334e-08</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>output\20251124154733-1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>31000941.83922017</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4384291.540475608</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1979982.706515317</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6364274.246990925</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24636667.59222924</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>31000941.83922017</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>89.31500005722046</v>
+      </c>
+      <c r="X6" t="n">
+        <v>31000941.83922017</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>31000941.83922017</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>output\20251124155024-1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>31040662.90706227</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4281288.946172599</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1942698.931344788</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6223987.877517387</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>24816675.02954488</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>31040662.90706227</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>130.4100000858307</v>
+      </c>
+      <c r="X7" t="n">
+        <v>31040662.90706227</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>31040662.90706227</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>output\20251124155525-1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>30987652.8648506</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4258191.050652722</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1933368.36013195</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6191559.410784671</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>24796093.45406593</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30987652.8648506</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>122.9450001716614</v>
+      </c>
+      <c r="X8" t="n">
+        <v>30987652.8648506</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>30987652.8648506</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>output\20251124160842-1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30959129.28237454</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4359169.15221068</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1963377.311450383</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6322546.463661063</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24716580.784515</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-79997.96580152672</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30959129.28237454</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>105.6419999599457</v>
+      </c>
+      <c r="X9" t="n">
+        <v>30959129.28237454</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>30959129.28237454</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output\20251124161425-1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>30964808.25039138</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4499041.492336266</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2014162.38460092</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6513203.876937185</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24551599.1572656</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-99994.78381141051</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30964808.25039138</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>154.4060001373291</v>
+      </c>
+      <c r="X10" t="n">
+        <v>30964808.25039138</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>30964808.25039138</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>output\20251124162036-1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>30940692.3370577</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4493656.772911779</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2012207.262582002</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6505864.035493781</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24434828.30156392</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>30940692.3370577</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>144.8680000305176</v>
+      </c>
+      <c r="X11" t="n">
+        <v>30940692.3370577</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>30940692.3370577</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>output\20251124163605-1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30918737.3028838</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4494045.101743303</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2012348.274248886</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6506393.375992189</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>24412343.92689161</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30918737.3028838</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>14.51799988746643</v>
+      </c>
+      <c r="X12" t="n">
+        <v>30918737.3028838</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>30918737.3028838</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>output\20251124174424-1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>187512434.3101974</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4418774.70480085</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1984907.533202097</v>
+      </c>
+      <c r="F13" t="n">
+        <v>156600300</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6403682.238002947</v>
+      </c>
+      <c r="H13" t="n">
+        <v>156600300</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24588445.90318817</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-79993.83099381214</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>187512434.3101974</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>133.5259997844696</v>
+      </c>
+      <c r="X13" t="n">
+        <v>187512434.3101974</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>187512434.3101974</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/output/Summary.xlsx
+++ b/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1794,6 +1794,107 @@
         <v>1</v>
       </c>
       <c r="AE13" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>output\20251127154536-1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>187529033.7359362</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4497480.441085723</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2013576.258318128</v>
+      </c>
+      <c r="F14" t="n">
+        <v>156600300</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6511056.69940385</v>
+      </c>
+      <c r="H14" t="n">
+        <v>156600300</v>
+      </c>
+      <c r="I14" t="n">
+        <v>24467674.42935357</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-49997.39282129705</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>187529033.7359362</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>18.83299994468689</v>
+      </c>
+      <c r="X14" t="n">
+        <v>187529033.7359362</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>187529033.7359362</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/output/Summary.xlsx
+++ b/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,6 +1895,107 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>output\20251127175058-1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>414620441.1292335</v>
+      </c>
+      <c r="C15" t="n">
+        <v>79365784.38304926</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30887642.37892314</v>
+      </c>
+      <c r="F15" t="n">
+        <v>156600300</v>
+      </c>
+      <c r="G15" t="n">
+        <v>110253426.7619724</v>
+      </c>
+      <c r="H15" t="n">
+        <v>156600300</v>
+      </c>
+      <c r="I15" t="n">
+        <v>147768497.6529753</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1783.285714285714</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>414620441.1292335</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>121.7869999408722</v>
+      </c>
+      <c r="X15" t="n">
+        <v>414620441.1292324</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>414620441.1292335</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.072883605957031e-06</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/output/Summary.xlsx
+++ b/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1996,6 +1996,107 @@
         <v>1</v>
       </c>
       <c r="AE15" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>output\20251204144722-1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>414414127.083848</v>
+      </c>
+      <c r="C16" t="n">
+        <v>79413237.56534173</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>30905226.65789823</v>
+      </c>
+      <c r="F16" t="n">
+        <v>156600300</v>
+      </c>
+      <c r="G16" t="n">
+        <v>110318464.22324</v>
+      </c>
+      <c r="H16" t="n">
+        <v>156600300</v>
+      </c>
+      <c r="I16" t="n">
+        <v>147497146.1463223</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-1783.285714285714</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>414414127.083848</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>94.53399991989136</v>
+      </c>
+      <c r="X16" t="n">
+        <v>414414127.0838466</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>414414127.083848</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.430511474609375e-06</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/output/Summary.xlsx
+++ b/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2097,6 +2097,309 @@
         <v>1</v>
       </c>
       <c r="AE16" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>output\20251205113843-1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3696999.336956954</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.007158240613208921</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.007158240613208921</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3836999.009796476</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-139999.6799977628</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3696999.336956954</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.177999973297119</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3676881.849305025</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3696999.336956954</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20117.48765192879</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>output\20251205133221-1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>64748274.98479408</v>
+      </c>
+      <c r="C18" t="n">
+        <v>11582708.18136209</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.234020655272847</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3926754.62290082</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15509462.80426291</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.234020655272847</v>
+      </c>
+      <c r="I18" t="n">
+        <v>49238811.94651051</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>64748274.98479408</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>83.45899987220764</v>
+      </c>
+      <c r="X18" t="n">
+        <v>64748274.98479399</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>64748274.98479408</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.940696716308594e-08</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>output\20251205135606-1</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>64762961.79300305</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11758430.61511528</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2385114218090135</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3992938.368812331</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15751368.98392761</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2385114218090135</v>
+      </c>
+      <c r="I19" t="n">
+        <v>49011592.57056402</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>64762961.79300305</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>159.1280000209808</v>
+      </c>
+      <c r="X19" t="n">
+        <v>64762961.79300298</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>64762961.79300305</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.705522537231445e-08</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/output/Summary.xlsx
+++ b/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AE20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2400,6 +2400,107 @@
         <v>1</v>
       </c>
       <c r="AE19" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>output\20251205144145-1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>64713563.74372575</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11510221.19699504</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2346726031689292</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3919016.830410321</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15429238.02740537</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2346726031689292</v>
+      </c>
+      <c r="I20" t="n">
+        <v>49284325.48164778</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>64713563.74372575</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>106.3980000019073</v>
+      </c>
+      <c r="X20" t="n">
+        <v>64713563.74372575</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>64713563.74372575</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7.450580596923828e-09</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/output/Summary.xlsx
+++ b/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE20"/>
+  <dimension ref="A1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2501,6 +2501,410 @@
         <v>1</v>
       </c>
       <c r="AE20" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>output\20251205152749-1</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>167.2469999790192</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>output\20251205155024-1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>211.0829999446869</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>output\20251205160047-1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>86.45700001716614</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>output\20251205162442-1</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>618316432.9111403</v>
+      </c>
+      <c r="C24" t="n">
+        <v>115103298.74737</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>39190575.07494289</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>154293873.822313</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>464022559.0888274</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>618316432.9111403</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>205.5080001354218</v>
+      </c>
+      <c r="X24" t="n">
+        <v>618316432.9111403</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>618316432.9111403</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
         <v>-1</v>
       </c>
     </row>
